--- a/data/trans_orig/IP16B01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16B01-Estudios-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77159</t>
+          <t>77175</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164822</t>
+          <t>164294</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>19328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53963</t>
+          <t>54122</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120598</t>
+          <t>120580</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263835</t>
+          <t>263829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>23429</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44562</t>
+          <t>45056</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54253</t>
+          <t>54133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54893</t>
+          <t>54526</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60560</t>
+          <t>60411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102615</t>
+          <t>102995</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113336</t>
+          <t>113478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14997</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>15348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22872</t>
+          <t>22702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25742</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>38863</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47603</t>
+          <t>47595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73996</t>
+          <t>73677</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86422</t>
+          <t>86225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87123</t>
+          <t>87037</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96011</t>
+          <t>95751</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164724</t>
+          <t>165258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179957</t>
+          <t>180086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24211</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>15170</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33529</t>
+          <t>33256</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43057</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36894</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44238</t>
+          <t>44237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73305</t>
+          <t>73522</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85323</t>
+          <t>85775</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>15979</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22286</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>12523</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17089</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>8531</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23532</t>
+          <t>24004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29813</t>
+          <t>30276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56439</t>
+          <t>55837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67099</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53488</t>
+          <t>53546</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62610</t>
+          <t>62516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113939</t>
+          <t>113767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127644</t>
+          <t>127868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
